--- a/Normalization/Tag.xlsx
+++ b/Normalization/Tag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\peggy\Github\databaseproject-G9\Normalization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E132053C-7E96-498F-B63C-05F29B3937F0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD4CACB-4535-42F8-A716-3AFFA30CF8AD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -792,9 +792,6 @@
     <t>同居日常</t>
   </si>
   <si>
-    <t>穿越道以女遊戲裡變成狗狗是不是搞錯了什麼?</t>
-  </si>
-  <si>
     <t>奇幻校園</t>
   </si>
   <si>
@@ -950,6 +947,10 @@
   </si>
   <si>
     <t>tag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿越到乙女遊戲裡變成狗狗是不是搞錯了什麼?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1303,10 +1304,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1351,7 +1352,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1371,7 +1372,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1421,7 +1422,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
@@ -1431,7 +1432,7 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
@@ -1441,7 +1442,7 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -1471,7 +1472,7 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
@@ -1486,7 +1487,7 @@
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
@@ -1501,7 +1502,7 @@
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
@@ -1551,7 +1552,7 @@
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
@@ -1601,7 +1602,7 @@
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
@@ -1686,17 +1687,17 @@
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
@@ -1771,7 +1772,7 @@
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
@@ -1801,7 +1802,7 @@
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
@@ -1816,7 +1817,7 @@
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
@@ -1846,7 +1847,7 @@
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
@@ -1886,7 +1887,7 @@
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
@@ -1931,7 +1932,7 @@
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
@@ -1966,7 +1967,7 @@
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>255</v>
+        <v>307</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
@@ -2001,7 +2002,7 @@
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
@@ -2016,7 +2017,7 @@
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
@@ -2051,7 +2052,7 @@
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
@@ -2086,12 +2087,12 @@
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
@@ -2176,7 +2177,7 @@
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
@@ -2196,7 +2197,7 @@
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
@@ -2221,22 +2222,22 @@
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
@@ -2256,12 +2257,12 @@
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
@@ -2286,7 +2287,7 @@
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
@@ -2306,7 +2307,7 @@
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.25">
@@ -2336,7 +2337,7 @@
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.25">
@@ -2391,7 +2392,7 @@
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
@@ -2421,7 +2422,7 @@
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
@@ -2446,17 +2447,17 @@
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
@@ -2491,7 +2492,7 @@
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
@@ -2561,7 +2562,7 @@
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
@@ -2571,7 +2572,7 @@
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.25">
@@ -2596,7 +2597,7 @@
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
@@ -2691,7 +2692,7 @@
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.25">
@@ -2721,7 +2722,7 @@
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
@@ -2796,7 +2797,7 @@
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.25">
@@ -2826,17 +2827,17 @@
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>

--- a/Normalization/Tag.xlsx
+++ b/Normalization/Tag.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\peggy\Github\databaseproject-G9\Normalization\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E806BF-166B-4A33-B610-BC29DF220E45}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -19,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="367">
   <si>
     <t>異世界</t>
   </si>
@@ -966,9 +972,6 @@
   </si>
   <si>
     <t>少年</t>
-  </si>
-  <si>
-    <t>欄1</t>
   </si>
   <si>
     <t>少年</t>
@@ -1190,7 +1193,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1223,7 +1226,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1231,24 +1234,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1275,15 +1268,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表格1" displayName="表格1" ref="A1:C307" totalsRowShown="0" headerRowBorderDxfId="0">
-  <autoFilter ref="A1:C307"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表格1" displayName="表格1" ref="A1:B307" totalsRowShown="0" headerRowBorderDxfId="0">
+  <autoFilter ref="A1:B307" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState ref="A2:A307">
     <sortCondition ref="A1:A307"/>
   </sortState>
-  <tableColumns count="3">
-    <tableColumn id="1" name="tag"/>
-    <tableColumn id="3" name="正則化tag"/>
-    <tableColumn id="2" name="欄1"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="tag"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="正則化tag"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1544,32 +1536,29 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C307"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B307"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.125" customWidth="1"/>
+    <col min="1" max="1" width="28.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>305</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -1577,23 +1566,23 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>308</v>
       </c>
       <c r="B4" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>181</v>
       </c>
@@ -1601,7 +1590,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>250</v>
       </c>
@@ -1609,7 +1598,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>88</v>
       </c>
@@ -1617,7 +1606,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>207</v>
       </c>
@@ -1625,15 +1614,15 @@
         <v>207</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>240</v>
       </c>
       <c r="B9" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>271</v>
       </c>
@@ -1641,7 +1630,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>249</v>
       </c>
@@ -1649,7 +1638,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>229</v>
       </c>
@@ -1657,7 +1646,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>193</v>
       </c>
@@ -1665,7 +1654,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>275</v>
       </c>
@@ -1673,7 +1662,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>82</v>
       </c>
@@ -1681,7 +1670,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>140</v>
       </c>
@@ -1689,7 +1678,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>230</v>
       </c>
@@ -1697,7 +1686,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>202</v>
       </c>
@@ -1705,7 +1694,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>131</v>
       </c>
@@ -1713,7 +1702,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1721,7 +1710,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -1729,7 +1718,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>162</v>
       </c>
@@ -1737,7 +1726,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>210</v>
       </c>
@@ -1745,7 +1734,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>255</v>
       </c>
@@ -1753,23 +1742,23 @@
         <v>255</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>165</v>
       </c>
       <c r="B25" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>303</v>
       </c>
       <c r="B26" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -1777,7 +1766,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>256</v>
       </c>
@@ -1785,7 +1774,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>170</v>
       </c>
@@ -1793,7 +1782,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -1801,7 +1790,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>48</v>
       </c>
@@ -1809,15 +1798,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>208</v>
       </c>
@@ -1825,15 +1814,15 @@
         <v>208</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>269</v>
       </c>
       <c r="B34" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>46</v>
       </c>
@@ -1841,15 +1830,15 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>159</v>
       </c>
       <c r="B36" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>299</v>
       </c>
@@ -1857,15 +1846,15 @@
         <v>299</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>114</v>
       </c>
@@ -1873,7 +1862,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>298</v>
       </c>
@@ -1881,15 +1870,15 @@
         <v>298</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>98</v>
       </c>
       <c r="B41" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>172</v>
       </c>
@@ -1897,15 +1886,15 @@
         <v>172</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>138</v>
       </c>
       <c r="B43" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>183</v>
       </c>
@@ -1913,7 +1902,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>167</v>
       </c>
@@ -1921,47 +1910,47 @@
         <v>167</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>166</v>
       </c>
       <c r="B46" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>177</v>
       </c>
       <c r="B47" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>158</v>
       </c>
       <c r="B48" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>189</v>
       </c>
       <c r="B49" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>272</v>
       </c>
       <c r="B50" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>126</v>
       </c>
@@ -1969,7 +1958,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>196</v>
       </c>
@@ -1977,7 +1966,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>187</v>
       </c>
@@ -1985,7 +1974,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>99</v>
       </c>
@@ -1993,7 +1982,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>15</v>
       </c>
@@ -2001,7 +1990,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>118</v>
       </c>
@@ -2009,7 +1998,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -2017,31 +2006,31 @@
         <v>64</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>81</v>
       </c>
       <c r="B58" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>160</v>
       </c>
       <c r="B59" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>262</v>
       </c>
       <c r="B60" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -2049,7 +2038,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -2057,7 +2046,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>239</v>
       </c>
@@ -2065,15 +2054,15 @@
         <v>239</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>200</v>
       </c>
       <c r="B64" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>47</v>
       </c>
@@ -2081,15 +2070,15 @@
         <v>47</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>139</v>
       </c>
       <c r="B66" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>44</v>
       </c>
@@ -2097,15 +2086,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>4</v>
       </c>
       <c r="B68" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>164</v>
       </c>
@@ -2113,23 +2102,23 @@
         <v>164</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>220</v>
       </c>
       <c r="B70" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>143</v>
       </c>
       <c r="B71" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>219</v>
       </c>
@@ -2137,15 +2126,15 @@
         <v>219</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>251</v>
       </c>
       <c r="B73" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>77</v>
       </c>
@@ -2153,23 +2142,23 @@
         <v>77</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>253</v>
       </c>
       <c r="B75" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>128</v>
       </c>
       <c r="B76" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>276</v>
       </c>
@@ -2177,15 +2166,15 @@
         <v>276</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>294</v>
       </c>
       <c r="B78" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>257</v>
       </c>
@@ -2193,7 +2182,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>105</v>
       </c>
@@ -2201,7 +2190,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>179</v>
       </c>
@@ -2209,7 +2198,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>185</v>
       </c>
@@ -2217,7 +2206,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>34</v>
       </c>
@@ -2225,7 +2214,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>213</v>
       </c>
@@ -2233,15 +2222,15 @@
         <v>213</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>21</v>
       </c>
       <c r="B85" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>242</v>
       </c>
@@ -2249,7 +2238,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>86</v>
       </c>
@@ -2257,7 +2246,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>226</v>
       </c>
@@ -2265,7 +2254,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>45</v>
       </c>
@@ -2273,7 +2262,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>55</v>
       </c>
@@ -2281,23 +2270,23 @@
         <v>45</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>235</v>
       </c>
       <c r="B91" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>211</v>
       </c>
       <c r="B92" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>238</v>
       </c>
@@ -2305,15 +2294,15 @@
         <v>238</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>289</v>
       </c>
       <c r="B94" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>90</v>
       </c>
@@ -2321,7 +2310,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>136</v>
       </c>
@@ -2329,7 +2318,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>66</v>
       </c>
@@ -2337,7 +2326,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>35</v>
       </c>
@@ -2345,47 +2334,47 @@
         <v>35</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>206</v>
       </c>
       <c r="B99" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>254</v>
       </c>
       <c r="B100" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>53</v>
       </c>
       <c r="B101" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>120</v>
       </c>
       <c r="B102" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>259</v>
       </c>
       <c r="B103" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>188</v>
       </c>
@@ -2393,7 +2382,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>247</v>
       </c>
@@ -2401,7 +2390,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>50</v>
       </c>
@@ -2409,7 +2398,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>216</v>
       </c>
@@ -2417,7 +2406,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>111</v>
       </c>
@@ -2425,7 +2414,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>296</v>
       </c>
@@ -2433,7 +2422,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>190</v>
       </c>
@@ -2441,7 +2430,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>23</v>
       </c>
@@ -2449,7 +2438,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>68</v>
       </c>
@@ -2457,23 +2446,23 @@
         <v>68</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>252</v>
       </c>
       <c r="B113" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>10</v>
       </c>
       <c r="B114" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>246</v>
       </c>
@@ -2481,7 +2470,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>121</v>
       </c>
@@ -2489,15 +2478,15 @@
         <v>121</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>266</v>
       </c>
       <c r="B117" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>29</v>
       </c>
@@ -2505,7 +2494,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>168</v>
       </c>
@@ -2513,7 +2502,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>109</v>
       </c>
@@ -2521,7 +2510,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>101</v>
       </c>
@@ -2529,7 +2518,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>184</v>
       </c>
@@ -2537,7 +2526,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>30</v>
       </c>
@@ -2545,15 +2534,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>245</v>
       </c>
       <c r="B124" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>3</v>
       </c>
@@ -2561,39 +2550,39 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>263</v>
       </c>
       <c r="B126" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>95</v>
       </c>
       <c r="B127" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>156</v>
       </c>
       <c r="B128" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>28</v>
       </c>
       <c r="B129" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>1</v>
       </c>
@@ -2601,39 +2590,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>174</v>
       </c>
       <c r="B131" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>7</v>
       </c>
       <c r="B132" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>306</v>
       </c>
       <c r="B133" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>178</v>
       </c>
       <c r="B134" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>134</v>
       </c>
@@ -2641,7 +2630,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>41</v>
       </c>
@@ -2649,7 +2638,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>33</v>
       </c>
@@ -2657,7 +2646,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>24</v>
       </c>
@@ -2665,7 +2654,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>37</v>
       </c>
@@ -2673,7 +2662,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>279</v>
       </c>
@@ -2681,7 +2670,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>89</v>
       </c>
@@ -2689,15 +2678,15 @@
         <v>89</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>142</v>
       </c>
       <c r="B142" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>283</v>
       </c>
@@ -2705,7 +2694,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>228</v>
       </c>
@@ -2713,7 +2702,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>70</v>
       </c>
@@ -2721,15 +2710,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>171</v>
       </c>
       <c r="B146" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>145</v>
       </c>
@@ -2737,7 +2726,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>180</v>
       </c>
@@ -2745,39 +2734,39 @@
         <v>180</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>227</v>
       </c>
       <c r="B149" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>281</v>
       </c>
       <c r="B150" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>49</v>
       </c>
       <c r="B151" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>203</v>
       </c>
       <c r="B152" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>69</v>
       </c>
@@ -2785,7 +2774,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>40</v>
       </c>
@@ -2793,7 +2782,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>243</v>
       </c>
@@ -2801,7 +2790,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>85</v>
       </c>
@@ -2809,23 +2798,23 @@
         <v>85</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>285</v>
       </c>
       <c r="B157" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>260</v>
       </c>
       <c r="B158" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>123</v>
       </c>
@@ -2833,7 +2822,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>116</v>
       </c>
@@ -2841,23 +2830,23 @@
         <v>116</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>209</v>
       </c>
       <c r="B161" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>18</v>
       </c>
       <c r="B162" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>67</v>
       </c>
@@ -2865,7 +2854,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>92</v>
       </c>
@@ -2873,7 +2862,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>241</v>
       </c>
@@ -2881,7 +2870,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>231</v>
       </c>
@@ -2889,7 +2878,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>129</v>
       </c>
@@ -2897,7 +2886,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>103</v>
       </c>
@@ -2905,15 +2894,15 @@
         <v>103</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>199</v>
       </c>
       <c r="B169" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>173</v>
       </c>
@@ -2921,7 +2910,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>52</v>
       </c>
@@ -2929,39 +2918,39 @@
         <v>173</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>0</v>
       </c>
       <c r="B172" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>31</v>
       </c>
       <c r="B173" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>2</v>
       </c>
       <c r="B174" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>282</v>
       </c>
       <c r="B175" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>74</v>
       </c>
@@ -2969,7 +2958,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>12</v>
       </c>
@@ -2977,7 +2966,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>22</v>
       </c>
@@ -2985,23 +2974,23 @@
         <v>22</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>295</v>
       </c>
       <c r="B179" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>222</v>
       </c>
       <c r="B180" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>157</v>
       </c>
@@ -3009,39 +2998,39 @@
         <v>157</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>94</v>
       </c>
       <c r="B182" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>147</v>
       </c>
       <c r="B183" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>302</v>
       </c>
       <c r="B184" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>293</v>
       </c>
       <c r="B185" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>300</v>
       </c>
@@ -3049,7 +3038,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>268</v>
       </c>
@@ -3057,7 +3046,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>100</v>
       </c>
@@ -3065,15 +3054,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>146</v>
       </c>
       <c r="B189" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>122</v>
       </c>
@@ -3081,7 +3070,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>280</v>
       </c>
@@ -3089,7 +3078,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>286</v>
       </c>
@@ -3097,15 +3086,15 @@
         <v>286</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>224</v>
       </c>
       <c r="B193" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>201</v>
       </c>
@@ -3113,7 +3102,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>127</v>
       </c>
@@ -3121,15 +3110,15 @@
         <v>127</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>75</v>
       </c>
       <c r="B196" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>287</v>
       </c>
@@ -3137,7 +3126,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>106</v>
       </c>
@@ -3145,7 +3134,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>93</v>
       </c>
@@ -3153,23 +3142,23 @@
         <v>93</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>124</v>
       </c>
       <c r="B200" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>288</v>
       </c>
       <c r="B201" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>32</v>
       </c>
@@ -3177,7 +3166,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>14</v>
       </c>
@@ -3185,7 +3174,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>194</v>
       </c>
@@ -3193,7 +3182,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>244</v>
       </c>
@@ -3201,7 +3190,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>80</v>
       </c>
@@ -3209,71 +3198,71 @@
         <v>80</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>267</v>
       </c>
       <c r="B207" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>20</v>
       </c>
       <c r="B208" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>108</v>
       </c>
       <c r="B209" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>221</v>
       </c>
       <c r="B210" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>154</v>
       </c>
       <c r="B211" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>153</v>
       </c>
       <c r="B212" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>182</v>
       </c>
       <c r="B213" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>19</v>
       </c>
       <c r="B214" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>57</v>
       </c>
@@ -3281,15 +3270,15 @@
         <v>57</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>161</v>
       </c>
       <c r="B216" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>149</v>
       </c>
@@ -3297,7 +3286,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>284</v>
       </c>
@@ -3305,7 +3294,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>42</v>
       </c>
@@ -3313,7 +3302,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>218</v>
       </c>
@@ -3321,7 +3310,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>38</v>
       </c>
@@ -3329,7 +3318,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>234</v>
       </c>
@@ -3337,31 +3326,31 @@
         <v>234</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>151</v>
       </c>
       <c r="B223" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>292</v>
       </c>
       <c r="B224" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>195</v>
       </c>
       <c r="B225" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>232</v>
       </c>
@@ -3369,7 +3358,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>36</v>
       </c>
@@ -3377,15 +3366,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>223</v>
       </c>
       <c r="B228" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>273</v>
       </c>
@@ -3393,15 +3382,15 @@
         <v>273</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>278</v>
       </c>
       <c r="B230" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>270</v>
       </c>
@@ -3409,7 +3398,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>225</v>
       </c>
@@ -3417,23 +3406,23 @@
         <v>225</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>43</v>
       </c>
       <c r="B233" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>135</v>
       </c>
       <c r="B234" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>59</v>
       </c>
@@ -3441,7 +3430,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>13</v>
       </c>
@@ -3449,7 +3438,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>150</v>
       </c>
@@ -3457,7 +3446,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>297</v>
       </c>
@@ -3465,15 +3454,15 @@
         <v>297</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>130</v>
       </c>
       <c r="B239" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>137</v>
       </c>
@@ -3481,15 +3470,15 @@
         <v>137</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>236</v>
       </c>
       <c r="B241" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>169</v>
       </c>
@@ -3497,7 +3486,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>73</v>
       </c>
@@ -3505,23 +3494,23 @@
         <v>73</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>205</v>
       </c>
       <c r="B244" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>125</v>
       </c>
       <c r="B245" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>78</v>
       </c>
@@ -3529,23 +3518,23 @@
         <v>78</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>176</v>
       </c>
       <c r="B247" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>112</v>
       </c>
       <c r="B248" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>65</v>
       </c>
@@ -3553,31 +3542,31 @@
         <v>65</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>212</v>
       </c>
       <c r="B251" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>261</v>
       </c>
       <c r="B252" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>217</v>
       </c>
@@ -3585,7 +3574,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>265</v>
       </c>
@@ -3593,39 +3582,39 @@
         <v>265</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>96</v>
       </c>
       <c r="B255" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>113</v>
       </c>
       <c r="B256" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>97</v>
       </c>
       <c r="B257" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>175</v>
       </c>
       <c r="B258" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>277</v>
       </c>
@@ -3633,7 +3622,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>71</v>
       </c>
@@ -3641,7 +3630,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>214</v>
       </c>
@@ -3649,7 +3638,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>51</v>
       </c>
@@ -3657,7 +3646,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>84</v>
       </c>
@@ -3665,7 +3654,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>25</v>
       </c>
@@ -3673,7 +3662,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>192</v>
       </c>
@@ -3681,7 +3670,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>56</v>
       </c>
@@ -3689,23 +3678,23 @@
         <v>56</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>163</v>
       </c>
       <c r="B267" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>155</v>
       </c>
@@ -3713,7 +3702,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>91</v>
       </c>
@@ -3721,7 +3710,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>132</v>
       </c>
@@ -3729,7 +3718,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>186</v>
       </c>
@@ -3737,15 +3726,15 @@
         <v>186</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>233</v>
       </c>
       <c r="B273" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>104</v>
       </c>
@@ -3753,15 +3742,15 @@
         <v>104</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>117</v>
       </c>
       <c r="B275" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>107</v>
       </c>
@@ -3769,7 +3758,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>197</v>
       </c>
@@ -3777,15 +3766,15 @@
         <v>197</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>301</v>
       </c>
       <c r="B278" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>237</v>
       </c>
@@ -3793,7 +3782,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>83</v>
       </c>
@@ -3801,7 +3790,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>79</v>
       </c>
@@ -3809,23 +3798,23 @@
         <v>79</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>141</v>
       </c>
       <c r="B282" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>87</v>
       </c>
       <c r="B283" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>258</v>
       </c>
@@ -3833,7 +3822,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>39</v>
       </c>
@@ -3841,23 +3830,23 @@
         <v>39</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>148</v>
       </c>
       <c r="B286" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>215</v>
       </c>
       <c r="B287" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>115</v>
       </c>
@@ -3865,15 +3854,15 @@
         <v>115</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>204</v>
       </c>
       <c r="B289" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>102</v>
       </c>
@@ -3881,7 +3870,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>191</v>
       </c>
@@ -3889,7 +3878,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>110</v>
       </c>
@@ -3897,15 +3886,15 @@
         <v>110</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>54</v>
       </c>
       <c r="B293" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>27</v>
       </c>
@@ -3913,7 +3902,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>119</v>
       </c>
@@ -3921,15 +3910,15 @@
         <v>119</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>144</v>
       </c>
       <c r="B296" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>152</v>
       </c>
@@ -3937,39 +3926,39 @@
         <v>152</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>26</v>
       </c>
       <c r="B298" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>274</v>
       </c>
       <c r="B299" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>198</v>
       </c>
       <c r="B300" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>133</v>
       </c>
       <c r="B301" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>58</v>
       </c>
@@ -3977,7 +3966,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>60</v>
       </c>
@@ -3985,7 +3974,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>76</v>
       </c>
@@ -3993,28 +3982,28 @@
         <v>76</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>264</v>
       </c>
       <c r="B305" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>290</v>
       </c>
       <c r="B306" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>291</v>
       </c>
       <c r="B307" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/Normalization/Tag.xlsx
+++ b/Normalization/Tag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\peggy\Github\databaseproject-G9\Normalization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1436E586-7713-4698-87B9-5DF43333ADFD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC67784-B5F9-46E0-9C8B-D608542D1F66}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="386">
   <si>
     <t>穿越</t>
   </si>
@@ -1385,10 +1385,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表格1" displayName="表格1" ref="A1:C332" totalsRowShown="0" headerRowBorderDxfId="1">
-  <autoFilter ref="A1:C332" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState ref="A2:C332">
-    <sortCondition ref="B1:B332"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表格1" displayName="表格1" ref="A1:C333" totalsRowShown="0" headerRowBorderDxfId="1">
+  <autoFilter ref="A1:C333" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState ref="A2:C333">
+    <sortCondition ref="B1:B333"/>
   </sortState>
   <tableColumns count="3">
     <tableColumn id="2" xr3:uid="{13079F51-54EE-4BC8-AD80-73ACC5FF8AF7}" name="tIndex" dataDxfId="0"/>
@@ -1662,14 +1662,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C332"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C333"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
     <col min="2" max="2" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>366</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1878,7 +1878,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
         <v>528</v>
       </c>
@@ -1999,7 +1999,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" s="5">
         <v>29</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>30</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" s="3">
         <v>31</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
         <v>531</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>32</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>33</v>
       </c>
@@ -2065,7 +2065,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>34</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>35</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>36</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>37</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>38</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>39</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>40</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>41</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
         <v>542</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>43</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>44</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49" s="3">
         <v>45</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
         <v>545</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>46</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>47</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>48</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>49</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>50</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>51</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>52</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>53</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>54</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>55</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>56</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>57</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A63" s="3">
         <v>58</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
         <v>558</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>59</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>60</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>61</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>62</v>
       </c>
@@ -2417,7 +2417,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A69" s="3">
         <v>63</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A70" s="3">
         <v>563</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>64</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A72" s="3">
         <v>65</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A73" s="3">
         <v>565</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>66</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>67</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>68</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>69</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>70</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>71</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>72</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>73</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>74</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>75</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>76</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>77</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>78</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>79</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>80</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>81</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>82</v>
       </c>
@@ -2659,7 +2659,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>83</v>
       </c>
@@ -2670,7 +2670,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>84</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>85</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>86</v>
       </c>
@@ -2703,7 +2703,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>87</v>
       </c>
@@ -2714,7 +2714,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>88</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>89</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>90</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>91</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>92</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>93</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>94</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>95</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>96</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>97</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A106" s="3">
         <v>98</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A107" s="3">
         <v>598</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A108" s="3">
         <v>99</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A109" s="3">
         <v>599</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>100</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>101</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>102</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>103</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>104</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>105</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>106</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>107</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>108</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>109</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>110</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>111</v>
       </c>
@@ -3000,7 +3000,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>112</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>113</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>114</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>115</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>116</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>117</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>118</v>
       </c>
@@ -3077,7 +3077,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>119</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>120</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>121</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>122</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>123</v>
       </c>
@@ -3132,7 +3132,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>124</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>125</v>
       </c>
@@ -3154,7 +3154,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A136" s="3">
         <v>126</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A137" s="3">
         <v>626</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A138" s="3">
         <v>127</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A139" s="3">
         <v>627</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>128</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>129</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>130</v>
       </c>
@@ -3231,1395 +3231,1395 @@
         <v>323</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A143" s="3">
         <v>131</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="3" t="s">
         <v>167</v>
       </c>
       <c r="C143" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A144" s="3">
-        <v>132</v>
+        <v>631</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>6</v>
+        <v>167</v>
       </c>
       <c r="C144" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A145" s="3">
+        <v>132</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C145" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A146" s="3">
         <v>632</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="B146" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C146" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A147">
         <v>133</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B147" t="s">
         <v>171</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C147" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A148">
         <v>134</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B148" t="s">
         <v>128</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C148" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A149">
         <v>135</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B149" t="s">
         <v>40</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C149" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A150">
         <v>136</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B150" t="s">
         <v>32</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C150" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A151">
         <v>137</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B151" t="s">
         <v>23</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C151" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A152">
         <v>138</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B152" t="s">
         <v>36</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C152" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A153">
         <v>139</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B153" t="s">
         <v>267</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C153" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A154">
         <v>140</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B154" t="s">
         <v>87</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C154" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A155">
         <v>141</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B155" t="s">
         <v>136</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C155" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A156">
         <v>142</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B156" t="s">
         <v>270</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C156" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A157">
         <v>143</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B157" t="s">
         <v>217</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C157" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A158">
         <v>144</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B158" t="s">
         <v>68</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C158" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A159" s="3">
         <v>145</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C158" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="3">
-        <v>645</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>164</v>
       </c>
       <c r="C159" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A160" s="3">
+        <v>645</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C160" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A161" s="3">
         <v>146</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C160" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="3">
-        <v>646</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>139</v>
       </c>
       <c r="C161" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A162" s="3">
+        <v>646</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C162" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A163">
         <v>147</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B163" t="s">
         <v>172</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C163" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A164">
         <v>148</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B164" t="s">
         <v>216</v>
       </c>
-      <c r="C163" t="s">
+      <c r="C164" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A165">
         <v>149</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B165" t="s">
         <v>383</v>
-      </c>
-      <c r="C164" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165">
-        <v>150</v>
-      </c>
-      <c r="B165" t="s">
-        <v>48</v>
       </c>
       <c r="C165" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A166">
+        <v>150</v>
+      </c>
+      <c r="B166" t="s">
+        <v>48</v>
+      </c>
+      <c r="C166" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A167">
         <v>151</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B167" t="s">
         <v>194</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C167" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A168">
         <v>152</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B168" t="s">
         <v>67</v>
       </c>
-      <c r="C167" t="s">
+      <c r="C168" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A169">
         <v>153</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B169" t="s">
         <v>39</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C169" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A170">
         <v>154</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B170" t="s">
         <v>232</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C170" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A171">
         <v>155</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B171" t="s">
         <v>83</v>
       </c>
-      <c r="C170" t="s">
+      <c r="C171" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A172">
         <v>156</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B172" t="s">
         <v>272</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C172" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A173">
         <v>157</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B173" t="s">
         <v>248</v>
       </c>
-      <c r="C172" t="s">
+      <c r="C173" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A174">
         <v>158</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B174" t="s">
         <v>118</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C174" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A175">
         <v>159</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B175" t="s">
         <v>112</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C175" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" s="3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A176" s="3">
         <v>160</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C175" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" s="3">
-        <v>660</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>352</v>
       </c>
       <c r="C176" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A177" s="3">
+        <v>660</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C177" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A178">
         <v>161</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B178" t="s">
         <v>17</v>
       </c>
-      <c r="C177" t="s">
+      <c r="C178" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A179">
         <v>162</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B179" t="s">
         <v>65</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C179" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A180">
         <v>163</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B180" t="s">
         <v>90</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C180" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A181">
         <v>164</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B181" t="s">
         <v>230</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C181" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A182">
         <v>165</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B182" t="s">
         <v>220</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C182" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A183">
         <v>166</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B183" t="s">
         <v>123</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C183" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A184">
         <v>167</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B184" t="s">
         <v>100</v>
       </c>
-      <c r="C183" t="s">
+      <c r="C184" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A185">
         <v>168</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B185" t="s">
         <v>190</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C185" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A186">
         <v>169</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B186" t="s">
         <v>166</v>
-      </c>
-      <c r="C185" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186">
-        <v>170</v>
-      </c>
-      <c r="B186" t="s">
-        <v>51</v>
       </c>
       <c r="C186" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A187">
+        <v>170</v>
+      </c>
+      <c r="B187" t="s">
+        <v>51</v>
+      </c>
+      <c r="C187" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A188">
         <v>171</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B188" t="s">
         <v>379</v>
       </c>
-      <c r="C187" t="s">
+      <c r="C188" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A189">
         <v>172</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B189" t="s">
         <v>30</v>
       </c>
-      <c r="C188" t="s">
+      <c r="C189" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A190">
         <v>173</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B190" t="s">
         <v>1</v>
-      </c>
-      <c r="C189" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190">
-        <v>174</v>
-      </c>
-      <c r="B190" t="s">
-        <v>269</v>
       </c>
       <c r="C190" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A191">
+        <v>174</v>
+      </c>
+      <c r="B191" t="s">
+        <v>269</v>
+      </c>
+      <c r="C191" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A192">
         <v>175</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B192" t="s">
         <v>354</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C192" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A193">
         <v>176</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B193" t="s">
         <v>11</v>
       </c>
-      <c r="C192" t="s">
+      <c r="C193" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A194">
         <v>177</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B194" t="s">
         <v>21</v>
       </c>
-      <c r="C193" t="s">
+      <c r="C194" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A195">
         <v>178</v>
       </c>
-      <c r="B194" s="5" t="s">
+      <c r="B195" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="C194" t="s">
+      <c r="C195" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A196" s="3">
         <v>179</v>
-      </c>
-      <c r="B195" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C195" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="3">
-        <v>679</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>211</v>
       </c>
       <c r="C196" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A197" s="3">
+        <v>679</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C197" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A198">
         <v>180</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B198" t="s">
         <v>151</v>
       </c>
-      <c r="C197" t="s">
+      <c r="C198" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A199">
         <v>181</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B199" t="s">
         <v>92</v>
-      </c>
-      <c r="C198" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="3">
-        <v>182</v>
-      </c>
-      <c r="B199" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="C199" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A200" s="3">
-        <v>682</v>
+        <v>182</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>141</v>
       </c>
       <c r="C200" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A201" s="3">
+        <v>682</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C201" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A202">
         <v>183</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B202" t="s">
         <v>287</v>
-      </c>
-      <c r="C201" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202">
-        <v>184</v>
-      </c>
-      <c r="B202" t="s">
-        <v>279</v>
       </c>
       <c r="C202" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A203">
+        <v>184</v>
+      </c>
+      <c r="B203" t="s">
+        <v>279</v>
+      </c>
+      <c r="C203" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A204">
         <v>185</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B204" t="s">
         <v>285</v>
       </c>
-      <c r="C203" t="s">
+      <c r="C204" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A205">
         <v>186</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B205" t="s">
         <v>256</v>
       </c>
-      <c r="C204" t="s">
+      <c r="C205" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A206">
         <v>187</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B206" t="s">
         <v>97</v>
       </c>
-      <c r="C205" t="s">
+      <c r="C206" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A207">
         <v>188</v>
       </c>
-      <c r="B206" t="s">
+      <c r="B207" t="s">
         <v>140</v>
       </c>
-      <c r="C206" t="s">
+      <c r="C207" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A208">
         <v>189</v>
       </c>
-      <c r="B207" t="s">
+      <c r="B208" t="s">
         <v>117</v>
       </c>
-      <c r="C207" t="s">
+      <c r="C208" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A209">
         <v>190</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B209" t="s">
         <v>268</v>
       </c>
-      <c r="C208" t="s">
+      <c r="C209" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A210">
         <v>191</v>
       </c>
-      <c r="B209" t="s">
+      <c r="B210" t="s">
         <v>273</v>
       </c>
-      <c r="C209" t="s">
+      <c r="C210" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A211">
         <v>192</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B211" t="s">
         <v>213</v>
       </c>
-      <c r="C210" t="s">
+      <c r="C211" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A212">
         <v>193</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B212" t="s">
         <v>192</v>
       </c>
-      <c r="C211" t="s">
+      <c r="C212" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A213">
         <v>194</v>
       </c>
-      <c r="B212" t="s">
+      <c r="B213" t="s">
         <v>121</v>
       </c>
-      <c r="C212" t="s">
+      <c r="C213" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A214">
         <v>195</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B214" t="s">
         <v>73</v>
       </c>
-      <c r="C213" t="s">
+      <c r="C214" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A215">
         <v>196</v>
       </c>
-      <c r="B214" t="s">
+      <c r="B215" t="s">
         <v>274</v>
-      </c>
-      <c r="C214" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215">
-        <v>197</v>
-      </c>
-      <c r="B215" t="s">
-        <v>103</v>
       </c>
       <c r="C215" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A216">
+        <v>197</v>
+      </c>
+      <c r="B216" t="s">
+        <v>103</v>
+      </c>
+      <c r="C216" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A217">
         <v>198</v>
       </c>
-      <c r="B216" t="s">
+      <c r="B217" t="s">
         <v>91</v>
       </c>
-      <c r="C216" t="s">
+      <c r="C217" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A218">
         <v>199</v>
       </c>
-      <c r="B217" t="s">
+      <c r="B218" t="s">
         <v>119</v>
       </c>
-      <c r="C217" t="s">
+      <c r="C218" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A219">
         <v>200</v>
       </c>
-      <c r="B218" t="s">
+      <c r="B219" t="s">
         <v>275</v>
       </c>
-      <c r="C218" t="s">
+      <c r="C219" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A220">
         <v>201</v>
       </c>
-      <c r="B219" t="s">
+      <c r="B220" t="s">
         <v>31</v>
       </c>
-      <c r="C219" t="s">
+      <c r="C220" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A221">
         <v>202</v>
       </c>
-      <c r="B220" t="s">
+      <c r="B221" t="s">
         <v>13</v>
       </c>
-      <c r="C220" t="s">
+      <c r="C221" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A222">
         <v>203</v>
       </c>
-      <c r="B221" t="s">
+      <c r="B222" t="s">
         <v>185</v>
       </c>
-      <c r="C221" t="s">
+      <c r="C222" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A223">
         <v>204</v>
       </c>
-      <c r="B222" t="s">
+      <c r="B223" t="s">
         <v>233</v>
       </c>
-      <c r="C222" t="s">
+      <c r="C223" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A224">
         <v>205</v>
       </c>
-      <c r="B223" t="s">
+      <c r="B224" t="s">
         <v>78</v>
       </c>
-      <c r="C223" t="s">
+      <c r="C224" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A225">
         <v>206</v>
       </c>
-      <c r="B224" t="s">
+      <c r="B225" t="s">
         <v>255</v>
       </c>
-      <c r="C224" t="s">
+      <c r="C225" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A226">
         <v>207</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B226" t="s">
         <v>19</v>
       </c>
-      <c r="C225" t="s">
+      <c r="C226" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A227">
         <v>208</v>
       </c>
-      <c r="B226" t="s">
+      <c r="B227" t="s">
         <v>104</v>
       </c>
-      <c r="C226" t="s">
+      <c r="C227" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" s="3">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A228" s="3">
         <v>209</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C227" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" s="3">
-        <v>709</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>210</v>
       </c>
       <c r="C228" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A229" s="3">
+        <v>709</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C229" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A230">
         <v>210</v>
       </c>
-      <c r="B229" t="s">
+      <c r="B230" t="s">
         <v>148</v>
-      </c>
-      <c r="C229" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230">
-        <v>211</v>
-      </c>
-      <c r="B230" t="s">
-        <v>147</v>
       </c>
       <c r="C230" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A231">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B231" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="C231" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A232">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B232" t="s">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="C232" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A233">
+        <v>213</v>
+      </c>
+      <c r="B233" t="s">
+        <v>18</v>
+      </c>
+      <c r="C233" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A234">
         <v>214</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B234" t="s">
         <v>55</v>
       </c>
-      <c r="C233" t="s">
+      <c r="C234" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A235">
         <v>215</v>
       </c>
-      <c r="B234" t="s">
+      <c r="B235" t="s">
         <v>155</v>
       </c>
-      <c r="C234" t="s">
+      <c r="C235" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A236">
         <v>216</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B236" t="s">
         <v>143</v>
       </c>
-      <c r="C235" t="s">
+      <c r="C236" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A237">
         <v>217</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B237" t="s">
         <v>271</v>
       </c>
-      <c r="C236" t="s">
+      <c r="C237" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A237">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A238">
         <v>218</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B238" t="s">
         <v>41</v>
       </c>
-      <c r="C237" t="s">
+      <c r="C238" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A238">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A239">
         <v>219</v>
       </c>
-      <c r="B238" t="s">
+      <c r="B239" t="s">
         <v>207</v>
       </c>
-      <c r="C238" t="s">
+      <c r="C239" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A239">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A240">
         <v>220</v>
       </c>
-      <c r="B239" t="s">
+      <c r="B240" t="s">
         <v>37</v>
       </c>
-      <c r="C239" t="s">
+      <c r="C240" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A240">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A241">
         <v>221</v>
       </c>
-      <c r="B240" t="s">
+      <c r="B241" t="s">
         <v>223</v>
       </c>
-      <c r="C240" t="s">
+      <c r="C241" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A241">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A242">
         <v>222</v>
       </c>
-      <c r="B241" t="s">
+      <c r="B242" t="s">
         <v>145</v>
       </c>
-      <c r="C241" t="s">
+      <c r="C242" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A242">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A243">
         <v>223</v>
       </c>
-      <c r="B242" t="s">
+      <c r="B243" t="s">
         <v>357</v>
       </c>
-      <c r="C242" t="s">
+      <c r="C243" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A244">
         <v>224</v>
       </c>
-      <c r="B243" t="s">
+      <c r="B244" t="s">
         <v>186</v>
       </c>
-      <c r="C243" t="s">
+      <c r="C244" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A244">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A245">
         <v>225</v>
       </c>
-      <c r="B244" t="s">
+      <c r="B245" t="s">
         <v>221</v>
       </c>
-      <c r="C244" t="s">
+      <c r="C245" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A245">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A246">
         <v>226</v>
       </c>
-      <c r="B245" t="s">
+      <c r="B246" t="s">
         <v>35</v>
       </c>
-      <c r="C245" t="s">
+      <c r="C246" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A247">
         <v>227</v>
       </c>
-      <c r="B246" t="s">
+      <c r="B247" t="s">
         <v>212</v>
       </c>
-      <c r="C246" t="s">
+      <c r="C247" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A247">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A248">
         <v>228</v>
       </c>
-      <c r="B247" t="s">
+      <c r="B248" t="s">
         <v>261</v>
       </c>
-      <c r="C247" t="s">
+      <c r="C248" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A249">
         <v>229</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B249" t="s">
         <v>266</v>
       </c>
-      <c r="C248" t="s">
+      <c r="C249" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A250">
         <v>230</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B250" t="s">
         <v>258</v>
       </c>
-      <c r="C249" t="s">
+      <c r="C250" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A250">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A251">
         <v>231</v>
       </c>
-      <c r="B250" t="s">
+      <c r="B251" t="s">
         <v>214</v>
       </c>
-      <c r="C250" t="s">
+      <c r="C251" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A251">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A252">
         <v>232</v>
       </c>
-      <c r="B251" t="s">
+      <c r="B252" t="s">
         <v>42</v>
       </c>
-      <c r="C251" t="s">
+      <c r="C252" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A252">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A253">
         <v>233</v>
       </c>
-      <c r="B252" t="s">
+      <c r="B253" t="s">
         <v>129</v>
       </c>
-      <c r="C252" t="s">
+      <c r="C253" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A254">
         <v>234</v>
       </c>
-      <c r="B253" t="s">
+      <c r="B254" t="s">
         <v>57</v>
       </c>
-      <c r="C253" t="s">
+      <c r="C254" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A255">
         <v>235</v>
       </c>
-      <c r="B254" t="s">
+      <c r="B255" t="s">
         <v>12</v>
       </c>
-      <c r="C254" t="s">
+      <c r="C255" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A255">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A256">
         <v>236</v>
       </c>
-      <c r="B255" t="s">
+      <c r="B256" t="s">
         <v>144</v>
       </c>
-      <c r="C255" t="s">
+      <c r="C256" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A256">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A257">
         <v>237</v>
       </c>
-      <c r="B256" t="s">
+      <c r="B257" t="s">
         <v>359</v>
       </c>
-      <c r="C256" t="s">
+      <c r="C257" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A258">
         <v>238</v>
       </c>
-      <c r="B257" t="s">
+      <c r="B258" t="s">
         <v>124</v>
       </c>
-      <c r="C257" t="s">
+      <c r="C258" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A258">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A259">
         <v>239</v>
       </c>
-      <c r="B258" t="s">
+      <c r="B259" t="s">
         <v>131</v>
       </c>
-      <c r="C258" t="s">
+      <c r="C259" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A259">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A260">
         <v>240</v>
       </c>
-      <c r="B259" t="s">
+      <c r="B260" t="s">
         <v>225</v>
       </c>
-      <c r="C259" t="s">
+      <c r="C260" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A260">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A261">
         <v>241</v>
       </c>
-      <c r="B260" t="s">
+      <c r="B261" t="s">
         <v>162</v>
       </c>
-      <c r="C260" t="s">
+      <c r="C261" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A261">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A262">
         <v>242</v>
       </c>
-      <c r="B261" t="s">
+      <c r="B262" t="s">
         <v>71</v>
       </c>
-      <c r="C261" t="s">
+      <c r="C262" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A262">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A263">
         <v>243</v>
       </c>
-      <c r="B262" t="s">
+      <c r="B263" t="s">
         <v>195</v>
       </c>
-      <c r="C262" t="s">
+      <c r="C263" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A264">
         <v>244</v>
       </c>
-      <c r="B263" t="s">
+      <c r="B264" t="s">
         <v>120</v>
       </c>
-      <c r="C263" t="s">
+      <c r="C264" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A264">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A265">
         <v>245</v>
       </c>
-      <c r="B264" t="s">
+      <c r="B265" t="s">
         <v>76</v>
       </c>
-      <c r="C264" t="s">
+      <c r="C265" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A266">
         <v>246</v>
       </c>
-      <c r="B265" t="s">
+      <c r="B266" t="s">
         <v>169</v>
       </c>
-      <c r="C265" t="s">
+      <c r="C266" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A266">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A267">
         <v>247</v>
       </c>
-      <c r="B266" t="s">
+      <c r="B267" t="s">
         <v>108</v>
       </c>
-      <c r="C266" t="s">
+      <c r="C267" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A267">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A268">
         <v>248</v>
       </c>
-      <c r="B267" t="s">
+      <c r="B268" t="s">
         <v>63</v>
       </c>
-      <c r="C267" t="s">
+      <c r="C268" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A268" s="3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A269" s="3">
         <v>249</v>
-      </c>
-      <c r="B268" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="C268" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A269" s="3">
-        <v>749</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>237</v>
@@ -4628,696 +4628,707 @@
         <v>370</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A270">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A270" s="3">
+        <v>749</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C270" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A271">
         <v>250</v>
       </c>
-      <c r="B270" t="s">
+      <c r="B271" t="s">
         <v>201</v>
-      </c>
-      <c r="C270" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A271">
-        <v>251</v>
-      </c>
-      <c r="B271" t="s">
-        <v>249</v>
       </c>
       <c r="C271" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A272">
+        <v>251</v>
+      </c>
+      <c r="B272" t="s">
+        <v>249</v>
+      </c>
+      <c r="C272" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A273">
         <v>252</v>
       </c>
-      <c r="B272" t="s">
+      <c r="B273" t="s">
         <v>206</v>
       </c>
-      <c r="C272" t="s">
+      <c r="C273" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A273">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A274">
         <v>253</v>
       </c>
-      <c r="B273" t="s">
+      <c r="B274" t="s">
         <v>253</v>
       </c>
-      <c r="C273" t="s">
+      <c r="C274" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A274">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A275">
         <v>254</v>
       </c>
-      <c r="B274" t="s">
+      <c r="B275" t="s">
         <v>385</v>
       </c>
-      <c r="C274" t="s">
+      <c r="C275" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A275">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A276">
         <v>255</v>
       </c>
-      <c r="B275" t="s">
+      <c r="B276" t="s">
         <v>109</v>
       </c>
-      <c r="C275" t="s">
+      <c r="C276" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A276">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A277">
         <v>256</v>
       </c>
-      <c r="B276" t="s">
+      <c r="B277" t="s">
         <v>94</v>
-      </c>
-      <c r="C276" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A277">
-        <v>257</v>
-      </c>
-      <c r="B277" t="s">
-        <v>168</v>
       </c>
       <c r="C277" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A278">
+        <v>257</v>
+      </c>
+      <c r="B278" t="s">
+        <v>168</v>
+      </c>
+      <c r="C278" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A279">
         <v>258</v>
       </c>
-      <c r="B278" t="s">
+      <c r="B279" t="s">
         <v>265</v>
       </c>
-      <c r="C278" t="s">
+      <c r="C279" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A279">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A280">
         <v>259</v>
       </c>
-      <c r="B279" t="s">
+      <c r="B280" t="s">
         <v>69</v>
       </c>
-      <c r="C279" t="s">
+      <c r="C280" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A280">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A281">
         <v>260</v>
       </c>
-      <c r="B280" t="s">
+      <c r="B281" t="s">
         <v>203</v>
       </c>
-      <c r="C280" t="s">
+      <c r="C281" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A281">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A282">
         <v>261</v>
       </c>
-      <c r="B281" t="s">
+      <c r="B282" t="s">
         <v>50</v>
       </c>
-      <c r="C281" t="s">
+      <c r="C282" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A282">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A283">
         <v>262</v>
       </c>
-      <c r="B282" t="s">
+      <c r="B283" t="s">
         <v>82</v>
-      </c>
-      <c r="C282" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283">
-        <v>263</v>
-      </c>
-      <c r="B283" t="s">
-        <v>24</v>
       </c>
       <c r="C283" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A284">
+        <v>263</v>
+      </c>
+      <c r="B284" t="s">
+        <v>24</v>
+      </c>
+      <c r="C284" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A285">
         <v>264</v>
       </c>
-      <c r="B284" t="s">
+      <c r="B285" t="s">
         <v>183</v>
       </c>
-      <c r="C284" t="s">
+      <c r="C285" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A285">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A286">
         <v>265</v>
       </c>
-      <c r="B285" t="s">
+      <c r="B286" t="s">
         <v>54</v>
       </c>
-      <c r="C285" t="s">
+      <c r="C286" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A286">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A287">
         <v>266</v>
       </c>
-      <c r="B286" t="s">
+      <c r="B287" t="s">
         <v>362</v>
       </c>
-      <c r="C286" t="s">
+      <c r="C287" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A287">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A288">
         <v>267</v>
       </c>
-      <c r="B287" t="s">
+      <c r="B288" t="s">
         <v>15</v>
       </c>
-      <c r="C287" t="s">
+      <c r="C288" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A288">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A289">
         <v>268</v>
       </c>
-      <c r="B288" t="s">
+      <c r="B289" t="s">
         <v>149</v>
       </c>
-      <c r="C288" t="s">
+      <c r="C289" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A289">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A290">
         <v>269</v>
       </c>
-      <c r="B289" t="s">
+      <c r="B290" t="s">
         <v>89</v>
       </c>
-      <c r="C289" t="s">
+      <c r="C290" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A290">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A291">
         <v>270</v>
       </c>
-      <c r="B290" t="s">
+      <c r="B291" t="s">
         <v>126</v>
       </c>
-      <c r="C290" t="s">
+      <c r="C291" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A291">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A292">
         <v>271</v>
       </c>
-      <c r="B291" t="s">
+      <c r="B292" t="s">
         <v>178</v>
       </c>
-      <c r="C291" t="s">
+      <c r="C292" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A292">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A293">
         <v>272</v>
       </c>
-      <c r="B292" t="s">
+      <c r="B293" t="s">
         <v>222</v>
       </c>
-      <c r="C292" t="s">
+      <c r="C293" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A293">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A294">
         <v>273</v>
       </c>
-      <c r="B293" t="s">
+      <c r="B294" t="s">
         <v>101</v>
       </c>
-      <c r="C293" t="s">
+      <c r="C294" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A294">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A295">
         <v>274</v>
       </c>
-      <c r="B294" t="s">
+      <c r="B295" t="s">
         <v>113</v>
       </c>
-      <c r="C294" t="s">
+      <c r="C295" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A295">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A296">
         <v>275</v>
       </c>
-      <c r="B295" t="s">
+      <c r="B296" t="s">
         <v>363</v>
       </c>
-      <c r="C295" t="s">
+      <c r="C296" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A296">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A297">
         <v>276</v>
       </c>
-      <c r="B296" t="s">
+      <c r="B297" t="s">
         <v>188</v>
       </c>
-      <c r="C296" t="s">
+      <c r="C297" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A297">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A298">
         <v>277</v>
       </c>
-      <c r="B297" t="s">
+      <c r="B298" t="s">
         <v>286</v>
       </c>
-      <c r="C297" t="s">
+      <c r="C298" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A298">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A299">
         <v>278</v>
       </c>
-      <c r="B298" t="s">
+      <c r="B299" t="s">
         <v>226</v>
       </c>
-      <c r="C298" t="s">
+      <c r="C299" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A299">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A300">
         <v>279</v>
       </c>
-      <c r="B299" t="s">
+      <c r="B300" t="s">
         <v>81</v>
       </c>
-      <c r="C299" t="s">
+      <c r="C300" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A300">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A301">
         <v>280</v>
       </c>
-      <c r="B300" t="s">
+      <c r="B301" t="s">
         <v>77</v>
       </c>
-      <c r="C300" t="s">
+      <c r="C301" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A301">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A302">
         <v>281</v>
       </c>
-      <c r="B301" t="s">
+      <c r="B302" t="s">
         <v>135</v>
       </c>
-      <c r="C301" t="s">
+      <c r="C302" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A302">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A303">
         <v>282</v>
       </c>
-      <c r="B302" t="s">
+      <c r="B303" t="s">
         <v>85</v>
       </c>
-      <c r="C302" t="s">
+      <c r="C303" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A303">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A304">
         <v>283</v>
       </c>
-      <c r="B303" t="s">
+      <c r="B304" t="s">
         <v>246</v>
       </c>
-      <c r="C303" t="s">
+      <c r="C304" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A304">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A305">
         <v>284</v>
       </c>
-      <c r="B304" t="s">
+      <c r="B305" t="s">
         <v>38</v>
       </c>
-      <c r="C304" t="s">
+      <c r="C305" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A305" s="3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A306" s="3">
         <v>285</v>
-      </c>
-      <c r="B305" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C305" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A306" s="3">
-        <v>785</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>142</v>
       </c>
       <c r="C306" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A307" s="3">
+        <v>785</v>
+      </c>
+      <c r="B307" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C307" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A307" s="3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A308" s="3">
         <v>286</v>
-      </c>
-      <c r="B307" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C307" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A308" s="3">
-        <v>786</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>204</v>
       </c>
       <c r="C308" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A309" s="3">
+        <v>786</v>
+      </c>
+      <c r="B309" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C309" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A309">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A310">
         <v>287</v>
       </c>
-      <c r="B309" t="s">
+      <c r="B310" t="s">
         <v>111</v>
       </c>
-      <c r="C309" t="s">
+      <c r="C310" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A310">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A311">
         <v>288</v>
       </c>
-      <c r="B310" t="s">
+      <c r="B311" t="s">
         <v>353</v>
       </c>
-      <c r="C310" t="s">
+      <c r="C311" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A311">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A312">
         <v>289</v>
       </c>
-      <c r="B311" t="s">
+      <c r="B312" t="s">
         <v>99</v>
       </c>
-      <c r="C311" t="s">
+      <c r="C312" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A312">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A313">
         <v>290</v>
       </c>
-      <c r="B312" t="s">
+      <c r="B313" t="s">
         <v>372</v>
       </c>
-      <c r="C312" t="s">
+      <c r="C313" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A313">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A314">
         <v>291</v>
       </c>
-      <c r="B313" t="s">
+      <c r="B314" t="s">
         <v>106</v>
-      </c>
-      <c r="C313" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A314">
-        <v>292</v>
-      </c>
-      <c r="B314" t="s">
-        <v>365</v>
       </c>
       <c r="C314" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A315">
+        <v>292</v>
+      </c>
+      <c r="B315" t="s">
+        <v>365</v>
+      </c>
+      <c r="C315" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A316">
         <v>293</v>
       </c>
-      <c r="B315" t="s">
+      <c r="B316" t="s">
         <v>26</v>
       </c>
-      <c r="C315" t="s">
+      <c r="C316" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A316">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A317">
         <v>294</v>
       </c>
-      <c r="B316" t="s">
+      <c r="B317" t="s">
         <v>375</v>
       </c>
-      <c r="C316" t="s">
+      <c r="C317" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A317">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A318">
         <v>295</v>
       </c>
-      <c r="B317" t="s">
+      <c r="B318" t="s">
         <v>138</v>
       </c>
-      <c r="C317" t="s">
+      <c r="C318" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A318">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A319">
         <v>296</v>
       </c>
-      <c r="B318" t="s">
+      <c r="B319" t="s">
         <v>146</v>
       </c>
-      <c r="C318" t="s">
+      <c r="C319" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A319">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A320">
         <v>297</v>
       </c>
-      <c r="B319" t="s">
+      <c r="B320" t="s">
         <v>25</v>
       </c>
-      <c r="C319" t="s">
+      <c r="C320" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A320" s="3">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A321" s="3">
         <v>298</v>
-      </c>
-      <c r="B320" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C320" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A321" s="3">
-        <v>798</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>262</v>
       </c>
       <c r="C321" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A322" s="3">
+        <v>798</v>
+      </c>
+      <c r="B322" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C322" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A322">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A323">
         <v>299</v>
       </c>
-      <c r="B322" t="s">
+      <c r="B323" t="s">
         <v>189</v>
       </c>
-      <c r="C322" t="s">
+      <c r="C323" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A323">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A324">
         <v>300</v>
       </c>
-      <c r="B323" t="s">
+      <c r="B324" t="s">
         <v>127</v>
       </c>
-      <c r="C323" t="s">
+      <c r="C324" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A324">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A325">
         <v>301</v>
       </c>
-      <c r="B324" t="s">
+      <c r="B325" t="s">
         <v>56</v>
-      </c>
-      <c r="C324" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A325" s="3">
-        <v>302</v>
-      </c>
-      <c r="B325" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="C325" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A326" s="3">
-        <v>802</v>
+        <v>302</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C326" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A327" s="3">
+        <v>802</v>
+      </c>
+      <c r="B327" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C327" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A327">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A328">
         <v>303</v>
       </c>
-      <c r="B327" t="s">
+      <c r="B328" t="s">
         <v>74</v>
       </c>
-      <c r="C327" t="s">
+      <c r="C328" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A328" s="3">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A329" s="3">
         <v>304</v>
-      </c>
-      <c r="B328" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="C328" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A329" s="3">
-        <v>804</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>252</v>
       </c>
       <c r="C329" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A330" s="3">
+        <v>804</v>
+      </c>
+      <c r="B330" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C330" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A330" s="3">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A331" s="3">
         <v>305</v>
-      </c>
-      <c r="B330" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C330" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A331" s="3">
-        <v>805</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>277</v>
       </c>
       <c r="C331" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A332" s="3">
+        <v>805</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C332" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A332">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A333">
         <v>306</v>
       </c>
-      <c r="B332" t="s">
+      <c r="B333" t="s">
         <v>278</v>
       </c>
-      <c r="C332" t="s">
+      <c r="C333" t="s">
         <v>346</v>
       </c>
     </row>
